--- a/6_Kalos_Data.xlsx
+++ b/6_Kalos_Data.xlsx
@@ -474,8 +474,8 @@
       <c r="H2" s="1">
         <v>0.3</v>
       </c>
-      <c r="I2" t="str">
-        <v/>
+      <c r="I2" s="1">
+        <v>0.16666666666666666</v>
       </c>
       <c r="J2" t="str">
         <v>Yes</v>
@@ -709,8 +709,8 @@
       <c r="H7" s="1">
         <v>0.05</v>
       </c>
-      <c r="I7" t="str">
-        <v/>
+      <c r="I7" s="1">
+        <v>0.16666666666666666</v>
       </c>
       <c r="J7" t="str">
         <v>Yes</v>
@@ -756,8 +756,8 @@
       <c r="H8" s="1">
         <v>0.3</v>
       </c>
-      <c r="I8" t="str">
-        <v/>
+      <c r="I8" s="1">
+        <v>0.16666666666666666</v>
       </c>
       <c r="J8" t="str">
         <v>Legacy</v>
@@ -991,8 +991,8 @@
       <c r="H13" s="1">
         <v>0.05</v>
       </c>
-      <c r="I13" t="str">
-        <v/>
+      <c r="I13" s="1">
+        <v>0.16666666666666666</v>
       </c>
       <c r="J13" t="str">
         <v>Yes</v>
@@ -1038,8 +1038,8 @@
       <c r="H14" s="1">
         <v>0.3</v>
       </c>
-      <c r="I14" t="str">
-        <v/>
+      <c r="I14" s="1">
+        <v>0.16666666666666666</v>
       </c>
       <c r="J14" t="str">
         <v>Yes</v>
@@ -1273,8 +1273,8 @@
       <c r="H19" s="1">
         <v>0.05</v>
       </c>
-      <c r="I19" t="str">
-        <v/>
+      <c r="I19" s="1">
+        <v>0.16666666666666666</v>
       </c>
       <c r="J19" t="str">
         <v>Yes</v>
@@ -1320,8 +1320,8 @@
       <c r="H20" s="1">
         <v>0.3</v>
       </c>
-      <c r="I20" t="str">
-        <v/>
+      <c r="I20" s="1">
+        <v>0.16666666666666666</v>
       </c>
       <c r="J20" t="str">
         <v>Yes</v>
@@ -1555,8 +1555,8 @@
       <c r="H25" s="1">
         <v>0.05</v>
       </c>
-      <c r="I25" t="str">
-        <v/>
+      <c r="I25" s="1">
+        <v>0.16666666666666666</v>
       </c>
       <c r="J25" t="str">
         <v>Legacy</v>
@@ -1602,8 +1602,8 @@
       <c r="H26" s="1">
         <v>0.3</v>
       </c>
-      <c r="I26" t="str">
-        <v/>
+      <c r="I26" s="1">
+        <v>0.16666666666666666</v>
       </c>
       <c r="J26" t="str">
         <v>Yes</v>
@@ -1837,8 +1837,8 @@
       <c r="H31" s="1">
         <v>0.05</v>
       </c>
-      <c r="I31" t="str">
-        <v/>
+      <c r="I31" s="1">
+        <v>0.16666666666666666</v>
       </c>
       <c r="J31" t="str">
         <v>Yes</v>
@@ -1931,8 +1931,8 @@
       <c r="H33" s="1">
         <v>0.3</v>
       </c>
-      <c r="I33" t="str">
-        <v/>
+      <c r="I33" s="1">
+        <v>0.16666666666666666</v>
       </c>
       <c r="J33" t="str">
         <v>Legacy</v>
@@ -2166,8 +2166,8 @@
       <c r="H38" s="1">
         <v>0.05</v>
       </c>
-      <c r="I38" t="str">
-        <v/>
+      <c r="I38" s="1">
+        <v>0.16666666666666666</v>
       </c>
       <c r="J38" t="str">
         <v>Yes</v>
@@ -2213,8 +2213,8 @@
       <c r="H39" s="1">
         <v>0.3</v>
       </c>
-      <c r="I39" t="str">
-        <v/>
+      <c r="I39" s="1">
+        <v>0.16666666666666666</v>
       </c>
       <c r="J39" t="str">
         <v>Yes</v>
@@ -2448,8 +2448,8 @@
       <c r="H44" s="1">
         <v>0.05</v>
       </c>
-      <c r="I44" t="str">
-        <v/>
+      <c r="I44" s="1">
+        <v>0.16666666666666666</v>
       </c>
       <c r="J44" t="str">
         <v>Yes</v>
@@ -2495,8 +2495,8 @@
       <c r="H45" s="1">
         <v>0.3</v>
       </c>
-      <c r="I45" t="str">
-        <v/>
+      <c r="I45" s="1">
+        <v>0.16666666666666666</v>
       </c>
       <c r="J45" t="str">
         <v>Yes</v>
@@ -2730,8 +2730,8 @@
       <c r="H50" s="1">
         <v>0.05</v>
       </c>
-      <c r="I50" t="str">
-        <v/>
+      <c r="I50" s="1">
+        <v>0.16666666666666666</v>
       </c>
       <c r="J50" t="str">
         <v>Yes</v>
@@ -2777,8 +2777,8 @@
       <c r="H51" s="1">
         <v>0.3</v>
       </c>
-      <c r="I51" t="str">
-        <v/>
+      <c r="I51" s="1">
+        <v>0.16666666666666666</v>
       </c>
       <c r="J51" t="str">
         <v>Yes</v>
@@ -3012,8 +3012,8 @@
       <c r="H56" s="1">
         <v>0.05</v>
       </c>
-      <c r="I56" t="str">
-        <v/>
+      <c r="I56" s="1">
+        <v>0.16666666666666666</v>
       </c>
       <c r="J56" t="str">
         <v>Yes</v>
@@ -3059,8 +3059,8 @@
       <c r="H57" s="1">
         <v>0.3</v>
       </c>
-      <c r="I57" t="str">
-        <v/>
+      <c r="I57" s="1">
+        <v>0.16666666666666666</v>
       </c>
       <c r="J57" t="str">
         <v>Yes</v>
@@ -3294,8 +3294,8 @@
       <c r="H62" s="1">
         <v>0.05</v>
       </c>
-      <c r="I62" t="str">
-        <v/>
+      <c r="I62" s="1">
+        <v>0.16666666666666666</v>
       </c>
       <c r="J62" t="str">
         <v>Yes</v>
@@ -3341,8 +3341,8 @@
       <c r="H63" s="1">
         <v>0.3</v>
       </c>
-      <c r="I63" t="str">
-        <v/>
+      <c r="I63" s="1">
+        <v>0.16666666666666666</v>
       </c>
       <c r="J63" t="str">
         <v>Yes</v>
@@ -3576,8 +3576,8 @@
       <c r="H68" s="1">
         <v>0.05</v>
       </c>
-      <c r="I68" t="str">
-        <v/>
+      <c r="I68" s="1">
+        <v>0.16666666666666666</v>
       </c>
       <c r="J68" t="str">
         <v>Yes</v>
@@ -3623,8 +3623,8 @@
       <c r="H69" s="1">
         <v>0.3</v>
       </c>
-      <c r="I69" t="str">
-        <v/>
+      <c r="I69" s="1">
+        <v>0.16666666666666666</v>
       </c>
       <c r="J69" t="str">
         <v>Legacy</v>
@@ -3858,8 +3858,8 @@
       <c r="H74" s="1">
         <v>0.05</v>
       </c>
-      <c r="I74" t="str">
-        <v/>
+      <c r="I74" s="1">
+        <v>0.16666666666666666</v>
       </c>
       <c r="J74" t="str">
         <v>Yes</v>
@@ -3905,8 +3905,8 @@
       <c r="H75" s="1">
         <v>0.3</v>
       </c>
-      <c r="I75" t="str">
-        <v/>
+      <c r="I75" s="1">
+        <v>0.16666666666666666</v>
       </c>
       <c r="J75" t="str">
         <v>Yes</v>
@@ -4140,8 +4140,8 @@
       <c r="H80" s="1">
         <v>0.05</v>
       </c>
-      <c r="I80" t="str">
-        <v/>
+      <c r="I80" s="1">
+        <v>0.16666666666666666</v>
       </c>
       <c r="J80" t="str">
         <v>Yes</v>
@@ -4187,8 +4187,8 @@
       <c r="H81" s="1">
         <v>0.3</v>
       </c>
-      <c r="I81" t="str">
-        <v/>
+      <c r="I81" s="1">
+        <v>0.16666666666666666</v>
       </c>
       <c r="J81" t="str">
         <v>Yes</v>
@@ -4422,8 +4422,8 @@
       <c r="H86" s="1">
         <v>0.05</v>
       </c>
-      <c r="I86" t="str">
-        <v/>
+      <c r="I86" s="1">
+        <v>0.16666666666666666</v>
       </c>
       <c r="J86" t="str">
         <v>Yes</v>
@@ -4469,8 +4469,8 @@
       <c r="H87" s="1">
         <v>0.3</v>
       </c>
-      <c r="I87" t="str">
-        <v/>
+      <c r="I87" s="1">
+        <v>0.16666666666666666</v>
       </c>
       <c r="J87" t="str">
         <v>Yes</v>
@@ -4704,8 +4704,8 @@
       <c r="H92" s="1">
         <v>0.05</v>
       </c>
-      <c r="I92" t="str">
-        <v/>
+      <c r="I92" s="1">
+        <v>0.16666666666666666</v>
       </c>
       <c r="J92" t="str">
         <v>Yes</v>
@@ -4751,8 +4751,8 @@
       <c r="H93" s="1">
         <v>0.3</v>
       </c>
-      <c r="I93" t="str">
-        <v/>
+      <c r="I93" s="1">
+        <v>0.16666666666666666</v>
       </c>
       <c r="J93" t="str">
         <v>Yes</v>
@@ -4986,8 +4986,8 @@
       <c r="H98" s="1">
         <v>0.05</v>
       </c>
-      <c r="I98" t="str">
-        <v/>
+      <c r="I98" s="1">
+        <v>0.16666666666666666</v>
       </c>
       <c r="J98" t="str">
         <v>Yes</v>
@@ -5033,8 +5033,8 @@
       <c r="H99" s="1">
         <v>0.3</v>
       </c>
-      <c r="I99" t="str">
-        <v/>
+      <c r="I99" s="1">
+        <v>0.16666666666666666</v>
       </c>
       <c r="J99" t="str">
         <v>Yes</v>
@@ -5268,8 +5268,8 @@
       <c r="H104" s="1">
         <v>0.05</v>
       </c>
-      <c r="I104" t="str">
-        <v/>
+      <c r="I104" s="1">
+        <v>0.16666666666666666</v>
       </c>
       <c r="J104" t="str">
         <v>Yes</v>
@@ -5315,8 +5315,8 @@
       <c r="H105" s="1">
         <v>0.3</v>
       </c>
-      <c r="I105" t="str">
-        <v/>
+      <c r="I105" s="1">
+        <v>0.16666666666666666</v>
       </c>
       <c r="J105" t="str">
         <v>Yes</v>
@@ -5550,8 +5550,8 @@
       <c r="H110" s="1">
         <v>0.05</v>
       </c>
-      <c r="I110" t="str">
-        <v/>
+      <c r="I110" s="1">
+        <v>0.16666666666666666</v>
       </c>
       <c r="J110" t="str">
         <v>Yes</v>
@@ -5597,8 +5597,8 @@
       <c r="H111" s="1">
         <v>0.3</v>
       </c>
-      <c r="I111" t="str">
-        <v/>
+      <c r="I111" s="1">
+        <v>0.16666666666666666</v>
       </c>
       <c r="J111" t="str">
         <v>Yes</v>
@@ -5832,8 +5832,8 @@
       <c r="H116" s="1">
         <v>0.05</v>
       </c>
-      <c r="I116" t="str">
-        <v/>
+      <c r="I116" s="1">
+        <v>0.16666666666666666</v>
       </c>
       <c r="J116" t="str">
         <v>Yes</v>
@@ -5879,8 +5879,8 @@
       <c r="H117" s="1">
         <v>0.3</v>
       </c>
-      <c r="I117" t="str">
-        <v/>
+      <c r="I117" s="1">
+        <v>0.16666666666666666</v>
       </c>
       <c r="J117" t="str">
         <v>Yes</v>
@@ -6114,8 +6114,8 @@
       <c r="H122" s="1">
         <v>0.05</v>
       </c>
-      <c r="I122" t="str">
-        <v/>
+      <c r="I122" s="1">
+        <v>0.16666666666666666</v>
       </c>
       <c r="J122" t="str">
         <v>Yes</v>
@@ -6208,8 +6208,8 @@
       <c r="H124" s="1">
         <v>0.3</v>
       </c>
-      <c r="I124" t="str">
-        <v/>
+      <c r="I124" s="1">
+        <v>0.16666666666666666</v>
       </c>
       <c r="J124" t="str">
         <v>Yes</v>
@@ -6443,8 +6443,8 @@
       <c r="H129" s="1">
         <v>0.05</v>
       </c>
-      <c r="I129" t="str">
-        <v/>
+      <c r="I129" s="1">
+        <v>0.16666666666666666</v>
       </c>
       <c r="J129" t="str">
         <v>Yes</v>
@@ -6490,8 +6490,8 @@
       <c r="H130" s="1">
         <v>0.3</v>
       </c>
-      <c r="I130" t="str">
-        <v/>
+      <c r="I130" s="1">
+        <v>0.16666666666666666</v>
       </c>
       <c r="J130" t="str">
         <v>Yes</v>
@@ -6725,8 +6725,8 @@
       <c r="H135" s="1">
         <v>0.05</v>
       </c>
-      <c r="I135" t="str">
-        <v/>
+      <c r="I135" s="1">
+        <v>0.16666666666666666</v>
       </c>
       <c r="J135" t="str">
         <v>Yes</v>
@@ -6772,8 +6772,8 @@
       <c r="H136" s="1">
         <v>0.3</v>
       </c>
-      <c r="I136" t="str">
-        <v/>
+      <c r="I136" s="1">
+        <v>0.16666666666666666</v>
       </c>
       <c r="J136" t="str">
         <v>Yes</v>
@@ -7007,8 +7007,8 @@
       <c r="H141" s="1">
         <v>0.05</v>
       </c>
-      <c r="I141" t="str">
-        <v/>
+      <c r="I141" s="1">
+        <v>0.16666666666666666</v>
       </c>
       <c r="J141" t="str">
         <v>Yes</v>
@@ -7054,8 +7054,8 @@
       <c r="H142" s="1">
         <v>0.3</v>
       </c>
-      <c r="I142" t="str">
-        <v/>
+      <c r="I142" s="1">
+        <v>0.16666666666666666</v>
       </c>
       <c r="J142" t="str">
         <v>Yes</v>
@@ -7289,8 +7289,8 @@
       <c r="H147" s="1">
         <v>0.05</v>
       </c>
-      <c r="I147" t="str">
-        <v/>
+      <c r="I147" s="1">
+        <v>0.16666666666666666</v>
       </c>
       <c r="J147" t="str">
         <v>Yes</v>
@@ -7383,8 +7383,8 @@
       <c r="H149" s="1">
         <v>0.3</v>
       </c>
-      <c r="I149" t="str">
-        <v/>
+      <c r="I149" s="1">
+        <v>0.16666666666666666</v>
       </c>
       <c r="J149" t="str">
         <v>Legacy</v>
@@ -7618,8 +7618,8 @@
       <c r="H154" s="1">
         <v>0.05</v>
       </c>
-      <c r="I154" t="str">
-        <v/>
+      <c r="I154" s="1">
+        <v>0.16666666666666666</v>
       </c>
       <c r="J154" t="str">
         <v>Legacy</v>
@@ -7665,8 +7665,8 @@
       <c r="H155" s="1">
         <v>0.3</v>
       </c>
-      <c r="I155" t="str">
-        <v/>
+      <c r="I155" s="1">
+        <v>0.16666666666666666</v>
       </c>
       <c r="J155" t="str">
         <v>Yes</v>
@@ -7900,8 +7900,8 @@
       <c r="H160" s="1">
         <v>0.05</v>
       </c>
-      <c r="I160" t="str">
-        <v/>
+      <c r="I160" s="1">
+        <v>0.16666666666666666</v>
       </c>
       <c r="J160" t="str">
         <v>Yes</v>
@@ -7947,8 +7947,8 @@
       <c r="H161" s="1">
         <v>0.3</v>
       </c>
-      <c r="I161" t="str">
-        <v/>
+      <c r="I161" s="1">
+        <v>0.2</v>
       </c>
       <c r="J161" t="str">
         <v>Yes</v>
@@ -8135,8 +8135,8 @@
       <c r="H165" s="1">
         <v>0.1</v>
       </c>
-      <c r="I165" t="str">
-        <v/>
+      <c r="I165" s="1">
+        <v>0.2</v>
       </c>
       <c r="J165" t="str">
         <v>Yes</v>
@@ -8229,8 +8229,8 @@
       <c r="H167" s="1">
         <v>0.3</v>
       </c>
-      <c r="I167" t="str">
-        <v/>
+      <c r="I167" s="1">
+        <v>0.2</v>
       </c>
       <c r="J167" t="str">
         <v>Yes</v>
@@ -8417,8 +8417,8 @@
       <c r="H171" s="1">
         <v>0.1</v>
       </c>
-      <c r="I171" t="str">
-        <v/>
+      <c r="I171" s="1">
+        <v>0.2</v>
       </c>
       <c r="J171" t="str">
         <v>Yes</v>
@@ -8464,8 +8464,8 @@
       <c r="H172" s="1">
         <v>0.3</v>
       </c>
-      <c r="I172" t="str">
-        <v/>
+      <c r="I172" s="1">
+        <v>0.2</v>
       </c>
       <c r="J172" t="str">
         <v>Yes</v>
@@ -8652,8 +8652,8 @@
       <c r="H176" s="1">
         <v>0.1</v>
       </c>
-      <c r="I176" t="str">
-        <v/>
+      <c r="I176" s="1">
+        <v>0.2</v>
       </c>
       <c r="J176" t="str">
         <v>Yes</v>
@@ -8699,8 +8699,8 @@
       <c r="H177" s="1">
         <v>0.3</v>
       </c>
-      <c r="I177" t="str">
-        <v/>
+      <c r="I177" s="1">
+        <v>0.2</v>
       </c>
       <c r="J177" t="str">
         <v>Yes</v>
@@ -8887,8 +8887,8 @@
       <c r="H181" s="1">
         <v>0.1</v>
       </c>
-      <c r="I181" t="str">
-        <v/>
+      <c r="I181" s="1">
+        <v>0.2</v>
       </c>
       <c r="J181" t="str">
         <v>Yes</v>
@@ -8981,8 +8981,8 @@
       <c r="H183" s="1">
         <v>0.3</v>
       </c>
-      <c r="I183" t="str">
-        <v/>
+      <c r="I183" s="1">
+        <v>0.2</v>
       </c>
       <c r="J183" t="str">
         <v>Yes</v>
@@ -9169,8 +9169,8 @@
       <c r="H187" s="1">
         <v>0.1</v>
       </c>
-      <c r="I187" t="str">
-        <v/>
+      <c r="I187" s="1">
+        <v>0.2</v>
       </c>
       <c r="J187" t="str">
         <v>Yes</v>
@@ -9216,8 +9216,8 @@
       <c r="H188" s="1">
         <v>0.3</v>
       </c>
-      <c r="I188" t="str">
-        <v/>
+      <c r="I188" s="1">
+        <v>0.2</v>
       </c>
       <c r="J188" t="str">
         <v>Yes</v>
@@ -9404,8 +9404,8 @@
       <c r="H192" s="1">
         <v>0.1</v>
       </c>
-      <c r="I192" t="str">
-        <v/>
+      <c r="I192" s="1">
+        <v>0.2</v>
       </c>
       <c r="J192" t="str">
         <v>Yes</v>
@@ -9498,8 +9498,8 @@
       <c r="H194" s="1">
         <v>0.3</v>
       </c>
-      <c r="I194" t="str">
-        <v/>
+      <c r="I194" s="1">
+        <v>0.2</v>
       </c>
       <c r="J194" t="str">
         <v>Yes</v>
@@ -9686,8 +9686,8 @@
       <c r="H198" s="1">
         <v>0.1</v>
       </c>
-      <c r="I198" t="str">
-        <v/>
+      <c r="I198" s="1">
+        <v>0.2</v>
       </c>
       <c r="J198" t="str">
         <v>Yes</v>
@@ -9733,8 +9733,8 @@
       <c r="H199" s="1">
         <v>0.3</v>
       </c>
-      <c r="I199" t="str">
-        <v/>
+      <c r="I199" s="1">
+        <v>0.2</v>
       </c>
       <c r="J199" t="str">
         <v>Yes</v>
@@ -9921,8 +9921,8 @@
       <c r="H203" s="1">
         <v>0.1</v>
       </c>
-      <c r="I203" t="str">
-        <v/>
+      <c r="I203" s="1">
+        <v>0.2</v>
       </c>
       <c r="J203" t="str">
         <v>Yes</v>
@@ -9968,8 +9968,8 @@
       <c r="H204" s="1">
         <v>0.3</v>
       </c>
-      <c r="I204" t="str">
-        <v/>
+      <c r="I204" s="1">
+        <v>0.2</v>
       </c>
       <c r="J204" t="str">
         <v>Yes</v>
@@ -10156,8 +10156,8 @@
       <c r="H208" s="1">
         <v>0.1</v>
       </c>
-      <c r="I208" t="str">
-        <v/>
+      <c r="I208" s="1">
+        <v>0.2</v>
       </c>
       <c r="J208" t="str">
         <v>Yes</v>
@@ -10203,8 +10203,8 @@
       <c r="H209" s="1">
         <v>0.3</v>
       </c>
-      <c r="I209" t="str">
-        <v/>
+      <c r="I209" s="1">
+        <v>0.2</v>
       </c>
       <c r="J209" t="str">
         <v>Yes</v>
@@ -10391,8 +10391,8 @@
       <c r="H213" s="1">
         <v>0.1</v>
       </c>
-      <c r="I213" t="str">
-        <v/>
+      <c r="I213" s="1">
+        <v>0.2</v>
       </c>
       <c r="J213" t="str">
         <v>Yes</v>
@@ -10438,8 +10438,8 @@
       <c r="H214" s="1">
         <v>0.3</v>
       </c>
-      <c r="I214" t="str">
-        <v/>
+      <c r="I214" s="1">
+        <v>0.2</v>
       </c>
       <c r="J214" t="str">
         <v>Yes</v>
@@ -10626,8 +10626,8 @@
       <c r="H218" s="1">
         <v>0.1</v>
       </c>
-      <c r="I218" t="str">
-        <v/>
+      <c r="I218" s="1">
+        <v>0.2</v>
       </c>
       <c r="J218" t="str">
         <v>Yes</v>
@@ -10673,8 +10673,8 @@
       <c r="H219" s="1">
         <v>0.3</v>
       </c>
-      <c r="I219" t="str">
-        <v/>
+      <c r="I219" s="1">
+        <v>0.2</v>
       </c>
       <c r="J219" t="str">
         <v>Yes</v>
@@ -10861,8 +10861,8 @@
       <c r="H223" s="1">
         <v>0.1</v>
       </c>
-      <c r="I223" t="str">
-        <v/>
+      <c r="I223" s="1">
+        <v>0.2</v>
       </c>
       <c r="J223" t="str">
         <v>Yes</v>
@@ -10955,8 +10955,8 @@
       <c r="H225" s="1">
         <v>0.3</v>
       </c>
-      <c r="I225" t="str">
-        <v/>
+      <c r="I225" s="1">
+        <v>0.2</v>
       </c>
       <c r="J225" t="str">
         <v>Yes</v>
@@ -11143,8 +11143,8 @@
       <c r="H229" s="1">
         <v>0.1</v>
       </c>
-      <c r="I229" t="str">
-        <v/>
+      <c r="I229" s="1">
+        <v>0.2</v>
       </c>
       <c r="J229" t="str">
         <v>Yes</v>
@@ -11190,8 +11190,8 @@
       <c r="H230" s="1">
         <v>0.3</v>
       </c>
-      <c r="I230" t="str">
-        <v/>
+      <c r="I230" s="1">
+        <v>0.2</v>
       </c>
       <c r="J230" t="str">
         <v>Yes</v>
@@ -11378,8 +11378,8 @@
       <c r="H234" s="1">
         <v>0.1</v>
       </c>
-      <c r="I234" t="str">
-        <v/>
+      <c r="I234" s="1">
+        <v>0.2</v>
       </c>
       <c r="J234" t="str">
         <v>Yes</v>
@@ -11425,8 +11425,8 @@
       <c r="H235" s="1">
         <v>0.3</v>
       </c>
-      <c r="I235" t="str">
-        <v/>
+      <c r="I235" s="1">
+        <v>0.2</v>
       </c>
       <c r="J235" t="str">
         <v>Legacy</v>
@@ -11613,8 +11613,8 @@
       <c r="H239" s="1">
         <v>0.1</v>
       </c>
-      <c r="I239" t="str">
-        <v/>
+      <c r="I239" s="1">
+        <v>0.2</v>
       </c>
       <c r="J239" t="str">
         <v>Yes</v>
@@ -11660,8 +11660,8 @@
       <c r="H240" s="1">
         <v>0.3</v>
       </c>
-      <c r="I240" t="str">
-        <v/>
+      <c r="I240" s="1">
+        <v>0.2</v>
       </c>
       <c r="J240" t="str">
         <v>Yes</v>
@@ -11848,8 +11848,8 @@
       <c r="H244" s="1">
         <v>0.1</v>
       </c>
-      <c r="I244" t="str">
-        <v/>
+      <c r="I244" s="1">
+        <v>0.2</v>
       </c>
       <c r="J244" t="str">
         <v>Yes</v>
@@ -11895,8 +11895,8 @@
       <c r="H245" s="1">
         <v>0.3</v>
       </c>
-      <c r="I245" t="str">
-        <v/>
+      <c r="I245" s="1">
+        <v>0.2</v>
       </c>
       <c r="J245" t="str">
         <v>Yes</v>
@@ -12083,8 +12083,8 @@
       <c r="H249" s="1">
         <v>0.1</v>
       </c>
-      <c r="I249" t="str">
-        <v/>
+      <c r="I249" s="1">
+        <v>0.2</v>
       </c>
       <c r="J249" t="str">
         <v>Yes</v>
@@ -12130,8 +12130,8 @@
       <c r="H250" s="1">
         <v>0.3</v>
       </c>
-      <c r="I250" t="str">
-        <v/>
+      <c r="I250" s="1">
+        <v>0.2</v>
       </c>
       <c r="J250" t="str">
         <v>Yes</v>
@@ -12318,8 +12318,8 @@
       <c r="H254" s="1">
         <v>0.1</v>
       </c>
-      <c r="I254" t="str">
-        <v/>
+      <c r="I254" s="1">
+        <v>0.2</v>
       </c>
       <c r="J254" t="str">
         <v>Yes</v>
@@ -12365,8 +12365,8 @@
       <c r="H255" s="1">
         <v>0.3</v>
       </c>
-      <c r="I255" t="str">
-        <v/>
+      <c r="I255" s="1">
+        <v>0.2</v>
       </c>
       <c r="J255" t="str">
         <v>Yes</v>
@@ -12553,8 +12553,8 @@
       <c r="H259" s="1">
         <v>0.1</v>
       </c>
-      <c r="I259" t="str">
-        <v/>
+      <c r="I259" s="1">
+        <v>0.2</v>
       </c>
       <c r="J259" t="str">
         <v>Yes</v>
@@ -12647,8 +12647,8 @@
       <c r="H261" s="1">
         <v>0.3</v>
       </c>
-      <c r="I261" t="str">
-        <v/>
+      <c r="I261" s="1">
+        <v>0.2</v>
       </c>
       <c r="J261" t="str">
         <v>Yes</v>
@@ -12835,8 +12835,8 @@
       <c r="H265" s="1">
         <v>0.1</v>
       </c>
-      <c r="I265" t="str">
-        <v/>
+      <c r="I265" s="1">
+        <v>0.2</v>
       </c>
       <c r="J265" t="str">
         <v>Yes</v>
@@ -12882,8 +12882,8 @@
       <c r="H266" s="1">
         <v>0.3</v>
       </c>
-      <c r="I266" t="str">
-        <v/>
+      <c r="I266" s="1">
+        <v>0.2</v>
       </c>
       <c r="J266" t="str">
         <v>Yes</v>
@@ -13070,8 +13070,8 @@
       <c r="H270" s="1">
         <v>0.1</v>
       </c>
-      <c r="I270" t="str">
-        <v/>
+      <c r="I270" s="1">
+        <v>0.2</v>
       </c>
       <c r="J270" t="str">
         <v>Yes</v>
@@ -13117,8 +13117,8 @@
       <c r="H271" s="1">
         <v>0.3</v>
       </c>
-      <c r="I271" t="str">
-        <v/>
+      <c r="I271" s="1">
+        <v>0.2</v>
       </c>
       <c r="J271" t="str">
         <v>Yes</v>
@@ -13305,8 +13305,8 @@
       <c r="H275" s="1">
         <v>0.1</v>
       </c>
-      <c r="I275" t="str">
-        <v/>
+      <c r="I275" s="1">
+        <v>0.2</v>
       </c>
       <c r="J275" t="str">
         <v>Yes</v>
@@ -13352,8 +13352,8 @@
       <c r="H276" s="1">
         <v>0.3</v>
       </c>
-      <c r="I276" t="str">
-        <v/>
+      <c r="I276" s="1">
+        <v>0.2</v>
       </c>
       <c r="J276" t="str">
         <v>Yes</v>
@@ -13540,8 +13540,8 @@
       <c r="H280" s="1">
         <v>0.1</v>
       </c>
-      <c r="I280" t="str">
-        <v/>
+      <c r="I280" s="1">
+        <v>0.2</v>
       </c>
       <c r="J280" t="str">
         <v>Yes</v>
@@ -13587,8 +13587,8 @@
       <c r="H281" s="1">
         <v>0.3</v>
       </c>
-      <c r="I281" t="str">
-        <v/>
+      <c r="I281" s="1">
+        <v>0.2</v>
       </c>
       <c r="J281" t="str">
         <v>Legacy</v>
@@ -13775,8 +13775,8 @@
       <c r="H285" s="1">
         <v>0.1</v>
       </c>
-      <c r="I285" t="str">
-        <v/>
+      <c r="I285" s="1">
+        <v>0.2</v>
       </c>
       <c r="J285" t="str">
         <v>Yes</v>
@@ -13822,8 +13822,8 @@
       <c r="H286" s="1">
         <v>0.3</v>
       </c>
-      <c r="I286" t="str">
-        <v/>
+      <c r="I286" s="1">
+        <v>0.16666666666666666</v>
       </c>
       <c r="J286" t="str">
         <v>Yes</v>
@@ -14057,8 +14057,8 @@
       <c r="H291" s="1">
         <v>0.05</v>
       </c>
-      <c r="I291" t="str">
-        <v/>
+      <c r="I291" s="1">
+        <v>0.16666666666666666</v>
       </c>
       <c r="J291" t="str">
         <v>Yes</v>
@@ -14104,8 +14104,8 @@
       <c r="H292" s="1">
         <v>0.3</v>
       </c>
-      <c r="I292" t="str">
-        <v/>
+      <c r="I292" s="1">
+        <v>0.16666666666666666</v>
       </c>
       <c r="J292" t="str">
         <v>Yes</v>
@@ -14339,8 +14339,8 @@
       <c r="H297" s="1">
         <v>0.05</v>
       </c>
-      <c r="I297" t="str">
-        <v/>
+      <c r="I297" s="1">
+        <v>0.16666666666666666</v>
       </c>
       <c r="J297" t="str">
         <v>Yes</v>
@@ -14386,8 +14386,8 @@
       <c r="H298" s="1">
         <v>0.3</v>
       </c>
-      <c r="I298" t="str">
-        <v/>
+      <c r="I298" s="1">
+        <v>0.16666666666666666</v>
       </c>
       <c r="J298" t="str">
         <v>Yes</v>
@@ -14621,8 +14621,8 @@
       <c r="H303" s="1">
         <v>0.05</v>
       </c>
-      <c r="I303" t="str">
-        <v/>
+      <c r="I303" s="1">
+        <v>0.16666666666666666</v>
       </c>
       <c r="J303" t="str">
         <v>Yes</v>
@@ -14668,8 +14668,8 @@
       <c r="H304" s="1">
         <v>0.3</v>
       </c>
-      <c r="I304" t="str">
-        <v/>
+      <c r="I304" s="1">
+        <v>0.2</v>
       </c>
       <c r="J304" t="str">
         <v>Yes</v>
@@ -14856,8 +14856,8 @@
       <c r="H308" s="1">
         <v>0.1</v>
       </c>
-      <c r="I308" t="str">
-        <v/>
+      <c r="I308" s="1">
+        <v>0.2</v>
       </c>
       <c r="J308" t="str">
         <v>Yes</v>
@@ -15608,8 +15608,8 @@
       <c r="H324" s="1">
         <v>0.3</v>
       </c>
-      <c r="I324" t="str">
-        <v/>
+      <c r="I324" s="1">
+        <v>0.2</v>
       </c>
       <c r="J324" t="str">
         <v>Yes</v>
@@ -15796,8 +15796,8 @@
       <c r="H328" s="1">
         <v>0.1</v>
       </c>
-      <c r="I328" t="str">
-        <v/>
+      <c r="I328" s="1">
+        <v>0.2</v>
       </c>
       <c r="J328" t="str">
         <v>Yes</v>
@@ -15843,8 +15843,8 @@
       <c r="H329" s="1">
         <v>0.3</v>
       </c>
-      <c r="I329" t="str">
-        <v/>
+      <c r="I329" s="1">
+        <v>0.2</v>
       </c>
       <c r="J329" t="str">
         <v>Yes</v>
@@ -16031,8 +16031,8 @@
       <c r="H333" s="1">
         <v>0.1</v>
       </c>
-      <c r="I333" t="str">
-        <v/>
+      <c r="I333" s="1">
+        <v>0.2</v>
       </c>
       <c r="J333" t="str">
         <v>Yes</v>
@@ -16078,8 +16078,8 @@
       <c r="H334" s="1">
         <v>0.3</v>
       </c>
-      <c r="I334" t="str">
-        <v/>
+      <c r="I334" s="1">
+        <v>0.2</v>
       </c>
       <c r="J334" t="str">
         <v>Yes</v>
@@ -16266,8 +16266,8 @@
       <c r="H338" s="1">
         <v>0.1</v>
       </c>
-      <c r="I338" t="str">
-        <v/>
+      <c r="I338" s="1">
+        <v>0.2</v>
       </c>
       <c r="J338" t="str">
         <v>Yes</v>
@@ -16313,8 +16313,8 @@
       <c r="H339" s="1">
         <v>0.3</v>
       </c>
-      <c r="I339" t="str">
-        <v/>
+      <c r="I339" s="1">
+        <v>0.2</v>
       </c>
       <c r="J339" t="str">
         <v>Yes</v>
@@ -16501,8 +16501,8 @@
       <c r="H343" s="1">
         <v>0.1</v>
       </c>
-      <c r="I343" t="str">
-        <v/>
+      <c r="I343" s="1">
+        <v>0.2</v>
       </c>
       <c r="J343" t="str">
         <v>Yes</v>
@@ -16548,8 +16548,8 @@
       <c r="H344" s="1">
         <v>0.3</v>
       </c>
-      <c r="I344" t="str">
-        <v/>
+      <c r="I344" s="1">
+        <v>0.2</v>
       </c>
       <c r="J344" t="str">
         <v>Yes</v>
@@ -16736,8 +16736,8 @@
       <c r="H348" s="1">
         <v>0.1</v>
       </c>
-      <c r="I348" t="str">
-        <v/>
+      <c r="I348" s="1">
+        <v>0.2</v>
       </c>
       <c r="J348" t="str">
         <v>Yes</v>
@@ -16783,8 +16783,8 @@
       <c r="H349" s="1">
         <v>0.3</v>
       </c>
-      <c r="I349" t="str">
-        <v/>
+      <c r="I349" s="1">
+        <v>0.2</v>
       </c>
       <c r="J349" t="str">
         <v>Yes</v>
@@ -16971,8 +16971,8 @@
       <c r="H353" s="1">
         <v>0.1</v>
       </c>
-      <c r="I353" t="str">
-        <v/>
+      <c r="I353" s="1">
+        <v>0.2</v>
       </c>
       <c r="J353" t="str">
         <v>Yes</v>
@@ -17018,8 +17018,8 @@
       <c r="H354" s="1">
         <v>0.3</v>
       </c>
-      <c r="I354" t="str">
-        <v/>
+      <c r="I354" s="1">
+        <v>0.2</v>
       </c>
       <c r="J354" t="str">
         <v>Yes</v>
@@ -17206,8 +17206,8 @@
       <c r="H358" s="1">
         <v>0.1</v>
       </c>
-      <c r="I358" t="str">
-        <v/>
+      <c r="I358" s="1">
+        <v>0.2</v>
       </c>
       <c r="J358" t="str">
         <v>Yes</v>
@@ -17248,7 +17248,7 @@
         <v>100-105</v>
       </c>
       <c r="G359" t="str">
-        <v>1-3</v>
+        <v>100-105</v>
       </c>
       <c r="H359" s="1">
         <v>0.33</v>
@@ -17295,7 +17295,7 @@
         <v>100-105</v>
       </c>
       <c r="G360" t="str">
-        <v>1-3</v>
+        <v>100-105</v>
       </c>
       <c r="H360" s="1">
         <v>0.33</v>
@@ -17342,7 +17342,7 @@
         <v>100-105</v>
       </c>
       <c r="G361" t="str">
-        <v>1-3</v>
+        <v>100-105</v>
       </c>
       <c r="H361" s="1">
         <v>0.33</v>
@@ -17394,8 +17394,8 @@
       <c r="H362" s="1">
         <v>0.3</v>
       </c>
-      <c r="I362" t="str">
-        <v/>
+      <c r="I362" s="1">
+        <v>0.2</v>
       </c>
       <c r="J362" t="str">
         <v>Yes</v>
@@ -17582,8 +17582,8 @@
       <c r="H366" s="1">
         <v>0.1</v>
       </c>
-      <c r="I366" t="str">
-        <v/>
+      <c r="I366" s="1">
+        <v>0.2</v>
       </c>
       <c r="J366" t="str">
         <v>Yes</v>
@@ -17629,8 +17629,8 @@
       <c r="H367" s="1">
         <v>0.3</v>
       </c>
-      <c r="I367" t="str">
-        <v/>
+      <c r="I367" s="1">
+        <v>0.2</v>
       </c>
       <c r="J367" t="str">
         <v>Yes</v>
@@ -17817,8 +17817,8 @@
       <c r="H371" s="1">
         <v>0.1</v>
       </c>
-      <c r="I371" t="str">
-        <v/>
+      <c r="I371" s="1">
+        <v>0.2</v>
       </c>
       <c r="J371" t="str">
         <v>Yes</v>
@@ -17859,7 +17859,7 @@
         <v>110-114</v>
       </c>
       <c r="G372" t="str">
-        <v>1-3</v>
+        <v>110-114</v>
       </c>
       <c r="H372" s="1">
         <v>0.25</v>
@@ -17906,7 +17906,7 @@
         <v>110-114</v>
       </c>
       <c r="G373" t="str">
-        <v>1-3</v>
+        <v>110-114</v>
       </c>
       <c r="H373" s="1">
         <v>0.25</v>
@@ -17953,7 +17953,7 @@
         <v>110-114</v>
       </c>
       <c r="G374" t="str">
-        <v>1-3</v>
+        <v>110-114</v>
       </c>
       <c r="H374" s="1">
         <v>0.25</v>
@@ -18000,7 +18000,7 @@
         <v>115-115</v>
       </c>
       <c r="G375" t="str">
-        <v>1-3</v>
+        <v>115-115</v>
       </c>
       <c r="H375" s="1">
         <v>0.25</v>
@@ -18052,8 +18052,8 @@
       <c r="H376" s="1">
         <v>0.3</v>
       </c>
-      <c r="I376" t="str">
-        <v/>
+      <c r="I376" s="1">
+        <v>0.2</v>
       </c>
       <c r="J376" t="str">
         <v>Yes</v>
@@ -18240,8 +18240,8 @@
       <c r="H380" s="1">
         <v>0.1</v>
       </c>
-      <c r="I380" t="str">
-        <v/>
+      <c r="I380" s="1">
+        <v>0.2</v>
       </c>
       <c r="J380" t="str">
         <v>Yes</v>
@@ -18287,8 +18287,8 @@
       <c r="H381" s="1">
         <v>0.3</v>
       </c>
-      <c r="I381" t="str">
-        <v/>
+      <c r="I381" s="1">
+        <v>0.2</v>
       </c>
       <c r="J381" t="str">
         <v>Yes</v>
@@ -18475,8 +18475,8 @@
       <c r="H385" s="1">
         <v>0.1</v>
       </c>
-      <c r="I385" t="str">
-        <v/>
+      <c r="I385" s="1">
+        <v>0.2</v>
       </c>
       <c r="J385" t="str">
         <v>Yes</v>
@@ -18522,8 +18522,8 @@
       <c r="H386" s="1">
         <v>0.3</v>
       </c>
-      <c r="I386" t="str">
-        <v/>
+      <c r="I386" s="1">
+        <v>0.2</v>
       </c>
       <c r="J386" t="str">
         <v>Yes</v>
@@ -18710,8 +18710,8 @@
       <c r="H390" s="1">
         <v>0.1</v>
       </c>
-      <c r="I390" t="str">
-        <v/>
+      <c r="I390" s="1">
+        <v>0.2</v>
       </c>
       <c r="J390" t="str">
         <v>Yes</v>
@@ -18752,7 +18752,7 @@
         <v>95-105</v>
       </c>
       <c r="G391" t="str">
-        <v>1-3</v>
+        <v>95-105</v>
       </c>
       <c r="H391" s="1">
         <v>0.25</v>
@@ -18799,7 +18799,7 @@
         <v>95-105</v>
       </c>
       <c r="G392" t="str">
-        <v>1-3</v>
+        <v>95-105</v>
       </c>
       <c r="H392" s="1">
         <v>0.25</v>
@@ -18846,7 +18846,7 @@
         <v>95-105</v>
       </c>
       <c r="G393" t="str">
-        <v>1-3</v>
+        <v>95-105</v>
       </c>
       <c r="H393" s="1">
         <v>0.25</v>
@@ -18893,7 +18893,7 @@
         <v>95-105</v>
       </c>
       <c r="G394" t="str">
-        <v>1-3</v>
+        <v>95-105</v>
       </c>
       <c r="H394" s="1">
         <v>0.25</v>
@@ -18945,8 +18945,8 @@
       <c r="H395" s="1">
         <v>0.3</v>
       </c>
-      <c r="I395" t="str">
-        <v/>
+      <c r="I395" s="1">
+        <v>0.2</v>
       </c>
       <c r="J395" t="str">
         <v>Yes</v>
@@ -19133,8 +19133,8 @@
       <c r="H399" s="1">
         <v>0.1</v>
       </c>
-      <c r="I399" t="str">
-        <v/>
+      <c r="I399" s="1">
+        <v>0.2</v>
       </c>
       <c r="J399" t="str">
         <v>Yes</v>
@@ -19180,8 +19180,8 @@
       <c r="H400" s="1">
         <v>0.3</v>
       </c>
-      <c r="I400" t="str">
-        <v/>
+      <c r="I400" s="1">
+        <v>0.2</v>
       </c>
       <c r="J400" t="str">
         <v>Yes</v>
@@ -19368,8 +19368,8 @@
       <c r="H404" s="1">
         <v>0.1</v>
       </c>
-      <c r="I404" t="str">
-        <v/>
+      <c r="I404" s="1">
+        <v>0.2</v>
       </c>
       <c r="J404" t="str">
         <v>Yes</v>
@@ -19415,8 +19415,8 @@
       <c r="H405" s="1">
         <v>0.3</v>
       </c>
-      <c r="I405" t="str">
-        <v/>
+      <c r="I405" s="1">
+        <v>0.2</v>
       </c>
       <c r="J405" t="str">
         <v>Yes</v>
@@ -19603,8 +19603,8 @@
       <c r="H409" s="1">
         <v>0.1</v>
       </c>
-      <c r="I409" t="str">
-        <v/>
+      <c r="I409" s="1">
+        <v>0.2</v>
       </c>
       <c r="J409" t="str">
         <v>Yes</v>
@@ -19736,7 +19736,7 @@
         <v>120-120</v>
       </c>
       <c r="G412" t="str">
-        <v>1-3</v>
+        <v>120-120</v>
       </c>
       <c r="H412" s="1">
         <v>0.33</v>
@@ -19783,7 +19783,7 @@
         <v>115-119</v>
       </c>
       <c r="G413" t="str">
-        <v>1-3</v>
+        <v>115-119</v>
       </c>
       <c r="H413" s="1">
         <v>0.33</v>
@@ -19830,7 +19830,7 @@
         <v>115-119</v>
       </c>
       <c r="G414" t="str">
-        <v>1-3</v>
+        <v>115-119</v>
       </c>
       <c r="H414" s="1">
         <v>0.33</v>

--- a/6_Kalos_Data.xlsx
+++ b/6_Kalos_Data.xlsx
@@ -475,7 +475,7 @@
         <v>0.3</v>
       </c>
       <c r="I2" s="1">
-        <v>0.16666666666666666</v>
+        <v>0.17</v>
       </c>
       <c r="J2" t="str">
         <v>Yes</v>
@@ -521,8 +521,8 @@
       <c r="H3" s="1">
         <v>0.25</v>
       </c>
-      <c r="I3" t="str">
-        <v/>
+      <c r="I3" s="1">
+        <v>0.17</v>
       </c>
       <c r="J3" t="str">
         <v>Yes</v>
@@ -662,8 +662,8 @@
       <c r="H6" s="1">
         <v>0.1</v>
       </c>
-      <c r="I6" t="str">
-        <v/>
+      <c r="I6" s="1">
+        <v>0.17</v>
       </c>
       <c r="J6" t="str">
         <v>Yes</v>
@@ -710,7 +710,7 @@
         <v>0.05</v>
       </c>
       <c r="I7" s="1">
-        <v>0.16666666666666666</v>
+        <v>0.15</v>
       </c>
       <c r="J7" t="str">
         <v>Yes</v>
@@ -757,7 +757,7 @@
         <v>0.3</v>
       </c>
       <c r="I8" s="1">
-        <v>0.16666666666666666</v>
+        <v>0.17</v>
       </c>
       <c r="J8" t="str">
         <v>Legacy</v>
@@ -803,8 +803,8 @@
       <c r="H9" s="1">
         <v>0.25</v>
       </c>
-      <c r="I9" t="str">
-        <v/>
+      <c r="I9" s="1">
+        <v>0.17</v>
       </c>
       <c r="J9" t="str">
         <v>Legacy</v>
@@ -944,8 +944,8 @@
       <c r="H12" s="1">
         <v>0.1</v>
       </c>
-      <c r="I12" t="str">
-        <v/>
+      <c r="I12" s="1">
+        <v>0.17</v>
       </c>
       <c r="J12" t="str">
         <v>Legacy</v>
@@ -992,7 +992,7 @@
         <v>0.05</v>
       </c>
       <c r="I13" s="1">
-        <v>0.16666666666666666</v>
+        <v>0.15</v>
       </c>
       <c r="J13" t="str">
         <v>Yes</v>
@@ -1039,7 +1039,7 @@
         <v>0.3</v>
       </c>
       <c r="I14" s="1">
-        <v>0.16666666666666666</v>
+        <v>0.17</v>
       </c>
       <c r="J14" t="str">
         <v>Yes</v>
@@ -1085,8 +1085,8 @@
       <c r="H15" s="1">
         <v>0.25</v>
       </c>
-      <c r="I15" t="str">
-        <v/>
+      <c r="I15" s="1">
+        <v>0.17</v>
       </c>
       <c r="J15" t="str">
         <v>Yes</v>
@@ -1226,8 +1226,8 @@
       <c r="H18" s="1">
         <v>0.1</v>
       </c>
-      <c r="I18" t="str">
-        <v/>
+      <c r="I18" s="1">
+        <v>0.17</v>
       </c>
       <c r="J18" t="str">
         <v>Yes</v>
@@ -1274,7 +1274,7 @@
         <v>0.05</v>
       </c>
       <c r="I19" s="1">
-        <v>0.16666666666666666</v>
+        <v>0.15</v>
       </c>
       <c r="J19" t="str">
         <v>Yes</v>
@@ -1321,7 +1321,7 @@
         <v>0.3</v>
       </c>
       <c r="I20" s="1">
-        <v>0.16666666666666666</v>
+        <v>0.17</v>
       </c>
       <c r="J20" t="str">
         <v>Yes</v>
@@ -1367,8 +1367,8 @@
       <c r="H21" s="1">
         <v>0.25</v>
       </c>
-      <c r="I21" t="str">
-        <v/>
+      <c r="I21" s="1">
+        <v>0.17</v>
       </c>
       <c r="J21" t="str">
         <v>Yes</v>
@@ -1508,8 +1508,8 @@
       <c r="H24" s="1">
         <v>0.1</v>
       </c>
-      <c r="I24" t="str">
-        <v/>
+      <c r="I24" s="1">
+        <v>0.17</v>
       </c>
       <c r="J24" t="str">
         <v>Yes</v>
@@ -1556,7 +1556,7 @@
         <v>0.05</v>
       </c>
       <c r="I25" s="1">
-        <v>0.16666666666666666</v>
+        <v>0.15</v>
       </c>
       <c r="J25" t="str">
         <v>Legacy</v>
@@ -1603,7 +1603,7 @@
         <v>0.3</v>
       </c>
       <c r="I26" s="1">
-        <v>0.16666666666666666</v>
+        <v>0.17</v>
       </c>
       <c r="J26" t="str">
         <v>Yes</v>
@@ -1649,8 +1649,8 @@
       <c r="H27" s="1">
         <v>0.25</v>
       </c>
-      <c r="I27" t="str">
-        <v/>
+      <c r="I27" s="1">
+        <v>0.17</v>
       </c>
       <c r="J27" t="str">
         <v>Yes</v>
@@ -1790,8 +1790,8 @@
       <c r="H30" s="1">
         <v>0.1</v>
       </c>
-      <c r="I30" t="str">
-        <v/>
+      <c r="I30" s="1">
+        <v>0.17</v>
       </c>
       <c r="J30" t="str">
         <v>Yes</v>
@@ -1838,7 +1838,7 @@
         <v>0.05</v>
       </c>
       <c r="I31" s="1">
-        <v>0.16666666666666666</v>
+        <v>0.15</v>
       </c>
       <c r="J31" t="str">
         <v>Yes</v>
@@ -1932,7 +1932,7 @@
         <v>0.3</v>
       </c>
       <c r="I33" s="1">
-        <v>0.16666666666666666</v>
+        <v>0.17</v>
       </c>
       <c r="J33" t="str">
         <v>Legacy</v>
@@ -1978,8 +1978,8 @@
       <c r="H34" s="1">
         <v>0.25</v>
       </c>
-      <c r="I34" t="str">
-        <v/>
+      <c r="I34" s="1">
+        <v>0.17</v>
       </c>
       <c r="J34" t="str">
         <v>Yes</v>
@@ -2119,8 +2119,8 @@
       <c r="H37" s="1">
         <v>0.1</v>
       </c>
-      <c r="I37" t="str">
-        <v/>
+      <c r="I37" s="1">
+        <v>0.17</v>
       </c>
       <c r="J37" t="str">
         <v>Yes</v>
@@ -2167,7 +2167,7 @@
         <v>0.05</v>
       </c>
       <c r="I38" s="1">
-        <v>0.16666666666666666</v>
+        <v>0.15</v>
       </c>
       <c r="J38" t="str">
         <v>Yes</v>
@@ -2214,7 +2214,7 @@
         <v>0.3</v>
       </c>
       <c r="I39" s="1">
-        <v>0.16666666666666666</v>
+        <v>0.17</v>
       </c>
       <c r="J39" t="str">
         <v>Yes</v>
@@ -2260,8 +2260,8 @@
       <c r="H40" s="1">
         <v>0.25</v>
       </c>
-      <c r="I40" t="str">
-        <v/>
+      <c r="I40" s="1">
+        <v>0.17</v>
       </c>
       <c r="J40" t="str">
         <v>Yes</v>
@@ -2401,8 +2401,8 @@
       <c r="H43" s="1">
         <v>0.1</v>
       </c>
-      <c r="I43" t="str">
-        <v/>
+      <c r="I43" s="1">
+        <v>0.17</v>
       </c>
       <c r="J43" t="str">
         <v>Legacy</v>
@@ -2449,7 +2449,7 @@
         <v>0.05</v>
       </c>
       <c r="I44" s="1">
-        <v>0.16666666666666666</v>
+        <v>0.15</v>
       </c>
       <c r="J44" t="str">
         <v>Yes</v>
@@ -2496,7 +2496,7 @@
         <v>0.3</v>
       </c>
       <c r="I45" s="1">
-        <v>0.16666666666666666</v>
+        <v>0.17</v>
       </c>
       <c r="J45" t="str">
         <v>Yes</v>
@@ -2542,8 +2542,8 @@
       <c r="H46" s="1">
         <v>0.25</v>
       </c>
-      <c r="I46" t="str">
-        <v/>
+      <c r="I46" s="1">
+        <v>0.17</v>
       </c>
       <c r="J46" t="str">
         <v>Yes</v>
@@ -2683,8 +2683,8 @@
       <c r="H49" s="1">
         <v>0.1</v>
       </c>
-      <c r="I49" t="str">
-        <v/>
+      <c r="I49" s="1">
+        <v>0.17</v>
       </c>
       <c r="J49" t="str">
         <v>Yes</v>
@@ -2731,7 +2731,7 @@
         <v>0.05</v>
       </c>
       <c r="I50" s="1">
-        <v>0.16666666666666666</v>
+        <v>0.15</v>
       </c>
       <c r="J50" t="str">
         <v>Yes</v>
@@ -2778,7 +2778,7 @@
         <v>0.3</v>
       </c>
       <c r="I51" s="1">
-        <v>0.16666666666666666</v>
+        <v>0.17</v>
       </c>
       <c r="J51" t="str">
         <v>Yes</v>
@@ -2824,8 +2824,8 @@
       <c r="H52" s="1">
         <v>0.25</v>
       </c>
-      <c r="I52" t="str">
-        <v/>
+      <c r="I52" s="1">
+        <v>0.17</v>
       </c>
       <c r="J52" t="str">
         <v>Yes</v>
@@ -2965,8 +2965,8 @@
       <c r="H55" s="1">
         <v>0.1</v>
       </c>
-      <c r="I55" t="str">
-        <v/>
+      <c r="I55" s="1">
+        <v>0.17</v>
       </c>
       <c r="J55" t="str">
         <v>Yes</v>
@@ -3013,7 +3013,7 @@
         <v>0.05</v>
       </c>
       <c r="I56" s="1">
-        <v>0.16666666666666666</v>
+        <v>0.15</v>
       </c>
       <c r="J56" t="str">
         <v>Yes</v>
@@ -3060,7 +3060,7 @@
         <v>0.3</v>
       </c>
       <c r="I57" s="1">
-        <v>0.16666666666666666</v>
+        <v>0.17</v>
       </c>
       <c r="J57" t="str">
         <v>Yes</v>
@@ -3106,8 +3106,8 @@
       <c r="H58" s="1">
         <v>0.25</v>
       </c>
-      <c r="I58" t="str">
-        <v/>
+      <c r="I58" s="1">
+        <v>0.17</v>
       </c>
       <c r="J58" t="str">
         <v>Yes</v>
@@ -3247,8 +3247,8 @@
       <c r="H61" s="1">
         <v>0.1</v>
       </c>
-      <c r="I61" t="str">
-        <v/>
+      <c r="I61" s="1">
+        <v>0.17</v>
       </c>
       <c r="J61" t="str">
         <v>Yes</v>
@@ -3295,7 +3295,7 @@
         <v>0.05</v>
       </c>
       <c r="I62" s="1">
-        <v>0.16666666666666666</v>
+        <v>0.15</v>
       </c>
       <c r="J62" t="str">
         <v>Yes</v>
@@ -3342,7 +3342,7 @@
         <v>0.3</v>
       </c>
       <c r="I63" s="1">
-        <v>0.16666666666666666</v>
+        <v>0.17</v>
       </c>
       <c r="J63" t="str">
         <v>Yes</v>
@@ -3388,8 +3388,8 @@
       <c r="H64" s="1">
         <v>0.25</v>
       </c>
-      <c r="I64" t="str">
-        <v/>
+      <c r="I64" s="1">
+        <v>0.17</v>
       </c>
       <c r="J64" t="str">
         <v>Yes</v>
@@ -3529,8 +3529,8 @@
       <c r="H67" s="1">
         <v>0.1</v>
       </c>
-      <c r="I67" t="str">
-        <v/>
+      <c r="I67" s="1">
+        <v>0.17</v>
       </c>
       <c r="J67" t="str">
         <v>Yes</v>
@@ -3577,7 +3577,7 @@
         <v>0.05</v>
       </c>
       <c r="I68" s="1">
-        <v>0.16666666666666666</v>
+        <v>0.15</v>
       </c>
       <c r="J68" t="str">
         <v>Yes</v>
@@ -3624,7 +3624,7 @@
         <v>0.3</v>
       </c>
       <c r="I69" s="1">
-        <v>0.16666666666666666</v>
+        <v>0.17</v>
       </c>
       <c r="J69" t="str">
         <v>Legacy</v>
@@ -3670,8 +3670,8 @@
       <c r="H70" s="1">
         <v>0.25</v>
       </c>
-      <c r="I70" t="str">
-        <v/>
+      <c r="I70" s="1">
+        <v>0.17</v>
       </c>
       <c r="J70" t="str">
         <v>Yes</v>
@@ -3811,8 +3811,8 @@
       <c r="H73" s="1">
         <v>0.1</v>
       </c>
-      <c r="I73" t="str">
-        <v/>
+      <c r="I73" s="1">
+        <v>0.17</v>
       </c>
       <c r="J73" t="str">
         <v>Yes</v>
@@ -3859,7 +3859,7 @@
         <v>0.05</v>
       </c>
       <c r="I74" s="1">
-        <v>0.16666666666666666</v>
+        <v>0.15</v>
       </c>
       <c r="J74" t="str">
         <v>Yes</v>
@@ -3906,7 +3906,7 @@
         <v>0.3</v>
       </c>
       <c r="I75" s="1">
-        <v>0.16666666666666666</v>
+        <v>0.17</v>
       </c>
       <c r="J75" t="str">
         <v>Yes</v>
@@ -3952,8 +3952,8 @@
       <c r="H76" s="1">
         <v>0.25</v>
       </c>
-      <c r="I76" t="str">
-        <v/>
+      <c r="I76" s="1">
+        <v>0.17</v>
       </c>
       <c r="J76" t="str">
         <v>Yes</v>
@@ -4093,8 +4093,8 @@
       <c r="H79" s="1">
         <v>0.1</v>
       </c>
-      <c r="I79" t="str">
-        <v/>
+      <c r="I79" s="1">
+        <v>0.17</v>
       </c>
       <c r="J79" t="str">
         <v>Yes</v>
@@ -4141,7 +4141,7 @@
         <v>0.05</v>
       </c>
       <c r="I80" s="1">
-        <v>0.16666666666666666</v>
+        <v>0.15</v>
       </c>
       <c r="J80" t="str">
         <v>Yes</v>
@@ -4188,7 +4188,7 @@
         <v>0.3</v>
       </c>
       <c r="I81" s="1">
-        <v>0.16666666666666666</v>
+        <v>0.17</v>
       </c>
       <c r="J81" t="str">
         <v>Yes</v>
@@ -4234,8 +4234,8 @@
       <c r="H82" s="1">
         <v>0.25</v>
       </c>
-      <c r="I82" t="str">
-        <v/>
+      <c r="I82" s="1">
+        <v>0.17</v>
       </c>
       <c r="J82" t="str">
         <v>Yes</v>
@@ -4375,8 +4375,8 @@
       <c r="H85" s="1">
         <v>0.1</v>
       </c>
-      <c r="I85" t="str">
-        <v/>
+      <c r="I85" s="1">
+        <v>0.17</v>
       </c>
       <c r="J85" t="str">
         <v>Yes</v>
@@ -4423,7 +4423,7 @@
         <v>0.05</v>
       </c>
       <c r="I86" s="1">
-        <v>0.16666666666666666</v>
+        <v>0.15</v>
       </c>
       <c r="J86" t="str">
         <v>Yes</v>
@@ -4470,7 +4470,7 @@
         <v>0.3</v>
       </c>
       <c r="I87" s="1">
-        <v>0.16666666666666666</v>
+        <v>0.17</v>
       </c>
       <c r="J87" t="str">
         <v>Yes</v>
@@ -4516,8 +4516,8 @@
       <c r="H88" s="1">
         <v>0.25</v>
       </c>
-      <c r="I88" t="str">
-        <v/>
+      <c r="I88" s="1">
+        <v>0.17</v>
       </c>
       <c r="J88" t="str">
         <v>Yes</v>
@@ -4657,8 +4657,8 @@
       <c r="H91" s="1">
         <v>0.1</v>
       </c>
-      <c r="I91" t="str">
-        <v/>
+      <c r="I91" s="1">
+        <v>0.17</v>
       </c>
       <c r="J91" t="str">
         <v>Yes</v>
@@ -4705,7 +4705,7 @@
         <v>0.05</v>
       </c>
       <c r="I92" s="1">
-        <v>0.16666666666666666</v>
+        <v>0.15</v>
       </c>
       <c r="J92" t="str">
         <v>Yes</v>
@@ -4752,7 +4752,7 @@
         <v>0.3</v>
       </c>
       <c r="I93" s="1">
-        <v>0.16666666666666666</v>
+        <v>0.17</v>
       </c>
       <c r="J93" t="str">
         <v>Yes</v>
@@ -4798,8 +4798,8 @@
       <c r="H94" s="1">
         <v>0.25</v>
       </c>
-      <c r="I94" t="str">
-        <v/>
+      <c r="I94" s="1">
+        <v>0.17</v>
       </c>
       <c r="J94" t="str">
         <v>Yes</v>
@@ -4939,8 +4939,8 @@
       <c r="H97" s="1">
         <v>0.1</v>
       </c>
-      <c r="I97" t="str">
-        <v/>
+      <c r="I97" s="1">
+        <v>0.17</v>
       </c>
       <c r="J97" t="str">
         <v>Yes</v>
@@ -4987,7 +4987,7 @@
         <v>0.05</v>
       </c>
       <c r="I98" s="1">
-        <v>0.16666666666666666</v>
+        <v>0.15</v>
       </c>
       <c r="J98" t="str">
         <v>Yes</v>
@@ -5034,7 +5034,7 @@
         <v>0.3</v>
       </c>
       <c r="I99" s="1">
-        <v>0.16666666666666666</v>
+        <v>0.17</v>
       </c>
       <c r="J99" t="str">
         <v>Yes</v>
@@ -5080,8 +5080,8 @@
       <c r="H100" s="1">
         <v>0.25</v>
       </c>
-      <c r="I100" t="str">
-        <v/>
+      <c r="I100" s="1">
+        <v>0.17</v>
       </c>
       <c r="J100" t="str">
         <v>Yes</v>
@@ -5221,8 +5221,8 @@
       <c r="H103" s="1">
         <v>0.1</v>
       </c>
-      <c r="I103" t="str">
-        <v/>
+      <c r="I103" s="1">
+        <v>0.17</v>
       </c>
       <c r="J103" t="str">
         <v>Yes</v>
@@ -5269,7 +5269,7 @@
         <v>0.05</v>
       </c>
       <c r="I104" s="1">
-        <v>0.16666666666666666</v>
+        <v>0.15</v>
       </c>
       <c r="J104" t="str">
         <v>Yes</v>
@@ -5316,7 +5316,7 @@
         <v>0.3</v>
       </c>
       <c r="I105" s="1">
-        <v>0.16666666666666666</v>
+        <v>0.17</v>
       </c>
       <c r="J105" t="str">
         <v>Yes</v>
@@ -5362,8 +5362,8 @@
       <c r="H106" s="1">
         <v>0.25</v>
       </c>
-      <c r="I106" t="str">
-        <v/>
+      <c r="I106" s="1">
+        <v>0.17</v>
       </c>
       <c r="J106" t="str">
         <v>Yes</v>
@@ -5503,8 +5503,8 @@
       <c r="H109" s="1">
         <v>0.1</v>
       </c>
-      <c r="I109" t="str">
-        <v/>
+      <c r="I109" s="1">
+        <v>0.17</v>
       </c>
       <c r="J109" t="str">
         <v>Yes</v>
@@ -5551,7 +5551,7 @@
         <v>0.05</v>
       </c>
       <c r="I110" s="1">
-        <v>0.16666666666666666</v>
+        <v>0.15</v>
       </c>
       <c r="J110" t="str">
         <v>Yes</v>
@@ -5598,7 +5598,7 @@
         <v>0.3</v>
       </c>
       <c r="I111" s="1">
-        <v>0.16666666666666666</v>
+        <v>0.17</v>
       </c>
       <c r="J111" t="str">
         <v>Yes</v>
@@ -5644,8 +5644,8 @@
       <c r="H112" s="1">
         <v>0.25</v>
       </c>
-      <c r="I112" t="str">
-        <v/>
+      <c r="I112" s="1">
+        <v>0.17</v>
       </c>
       <c r="J112" t="str">
         <v>Yes</v>
@@ -5785,8 +5785,8 @@
       <c r="H115" s="1">
         <v>0.1</v>
       </c>
-      <c r="I115" t="str">
-        <v/>
+      <c r="I115" s="1">
+        <v>0.17</v>
       </c>
       <c r="J115" t="str">
         <v>Yes</v>
@@ -5833,7 +5833,7 @@
         <v>0.05</v>
       </c>
       <c r="I116" s="1">
-        <v>0.16666666666666666</v>
+        <v>0.15</v>
       </c>
       <c r="J116" t="str">
         <v>Yes</v>
@@ -5880,7 +5880,7 @@
         <v>0.3</v>
       </c>
       <c r="I117" s="1">
-        <v>0.16666666666666666</v>
+        <v>0.17</v>
       </c>
       <c r="J117" t="str">
         <v>Yes</v>
@@ -5926,8 +5926,8 @@
       <c r="H118" s="1">
         <v>0.25</v>
       </c>
-      <c r="I118" t="str">
-        <v/>
+      <c r="I118" s="1">
+        <v>0.17</v>
       </c>
       <c r="J118" t="str">
         <v>Legacy</v>
@@ -6067,8 +6067,8 @@
       <c r="H121" s="1">
         <v>0.1</v>
       </c>
-      <c r="I121" t="str">
-        <v/>
+      <c r="I121" s="1">
+        <v>0.17</v>
       </c>
       <c r="J121" t="str">
         <v>Yes</v>
@@ -6115,7 +6115,7 @@
         <v>0.05</v>
       </c>
       <c r="I122" s="1">
-        <v>0.16666666666666666</v>
+        <v>0.15</v>
       </c>
       <c r="J122" t="str">
         <v>Yes</v>
@@ -6209,7 +6209,7 @@
         <v>0.3</v>
       </c>
       <c r="I124" s="1">
-        <v>0.16666666666666666</v>
+        <v>0.17</v>
       </c>
       <c r="J124" t="str">
         <v>Yes</v>
@@ -6255,8 +6255,8 @@
       <c r="H125" s="1">
         <v>0.25</v>
       </c>
-      <c r="I125" t="str">
-        <v/>
+      <c r="I125" s="1">
+        <v>0.17</v>
       </c>
       <c r="J125" t="str">
         <v>Legacy</v>
@@ -6396,8 +6396,8 @@
       <c r="H128" s="1">
         <v>0.1</v>
       </c>
-      <c r="I128" t="str">
-        <v/>
+      <c r="I128" s="1">
+        <v>0.17</v>
       </c>
       <c r="J128" t="str">
         <v>Yes</v>
@@ -6444,7 +6444,7 @@
         <v>0.05</v>
       </c>
       <c r="I129" s="1">
-        <v>0.16666666666666666</v>
+        <v>0.15</v>
       </c>
       <c r="J129" t="str">
         <v>Yes</v>
@@ -6491,7 +6491,7 @@
         <v>0.3</v>
       </c>
       <c r="I130" s="1">
-        <v>0.16666666666666666</v>
+        <v>0.17</v>
       </c>
       <c r="J130" t="str">
         <v>Yes</v>
@@ -6537,8 +6537,8 @@
       <c r="H131" s="1">
         <v>0.25</v>
       </c>
-      <c r="I131" t="str">
-        <v/>
+      <c r="I131" s="1">
+        <v>0.17</v>
       </c>
       <c r="J131" t="str">
         <v>Yes</v>
@@ -6678,8 +6678,8 @@
       <c r="H134" s="1">
         <v>0.1</v>
       </c>
-      <c r="I134" t="str">
-        <v/>
+      <c r="I134" s="1">
+        <v>0.17</v>
       </c>
       <c r="J134" t="str">
         <v>Yes</v>
@@ -6726,7 +6726,7 @@
         <v>0.05</v>
       </c>
       <c r="I135" s="1">
-        <v>0.16666666666666666</v>
+        <v>0.15</v>
       </c>
       <c r="J135" t="str">
         <v>Yes</v>
@@ -6773,7 +6773,7 @@
         <v>0.3</v>
       </c>
       <c r="I136" s="1">
-        <v>0.16666666666666666</v>
+        <v>0.17</v>
       </c>
       <c r="J136" t="str">
         <v>Yes</v>
@@ -6819,8 +6819,8 @@
       <c r="H137" s="1">
         <v>0.25</v>
       </c>
-      <c r="I137" t="str">
-        <v/>
+      <c r="I137" s="1">
+        <v>0.17</v>
       </c>
       <c r="J137" t="str">
         <v>Legacy</v>
@@ -6960,8 +6960,8 @@
       <c r="H140" s="1">
         <v>0.1</v>
       </c>
-      <c r="I140" t="str">
-        <v/>
+      <c r="I140" s="1">
+        <v>0.17</v>
       </c>
       <c r="J140" t="str">
         <v>Yes</v>
@@ -7008,7 +7008,7 @@
         <v>0.05</v>
       </c>
       <c r="I141" s="1">
-        <v>0.16666666666666666</v>
+        <v>0.15</v>
       </c>
       <c r="J141" t="str">
         <v>Yes</v>
@@ -7055,7 +7055,7 @@
         <v>0.3</v>
       </c>
       <c r="I142" s="1">
-        <v>0.16666666666666666</v>
+        <v>0.17</v>
       </c>
       <c r="J142" t="str">
         <v>Yes</v>
@@ -7101,8 +7101,8 @@
       <c r="H143" s="1">
         <v>0.25</v>
       </c>
-      <c r="I143" t="str">
-        <v/>
+      <c r="I143" s="1">
+        <v>0.17</v>
       </c>
       <c r="J143" t="str">
         <v>Yes</v>
@@ -7242,8 +7242,8 @@
       <c r="H146" s="1">
         <v>0.1</v>
       </c>
-      <c r="I146" t="str">
-        <v/>
+      <c r="I146" s="1">
+        <v>0.17</v>
       </c>
       <c r="J146" t="str">
         <v>Yes</v>
@@ -7290,7 +7290,7 @@
         <v>0.05</v>
       </c>
       <c r="I147" s="1">
-        <v>0.16666666666666666</v>
+        <v>0.15</v>
       </c>
       <c r="J147" t="str">
         <v>Yes</v>
@@ -7384,7 +7384,7 @@
         <v>0.3</v>
       </c>
       <c r="I149" s="1">
-        <v>0.16666666666666666</v>
+        <v>0.17</v>
       </c>
       <c r="J149" t="str">
         <v>Legacy</v>
@@ -7430,8 +7430,8 @@
       <c r="H150" s="1">
         <v>0.25</v>
       </c>
-      <c r="I150" t="str">
-        <v/>
+      <c r="I150" s="1">
+        <v>0.17</v>
       </c>
       <c r="J150" t="str">
         <v>Yes</v>
@@ -7571,8 +7571,8 @@
       <c r="H153" s="1">
         <v>0.1</v>
       </c>
-      <c r="I153" t="str">
-        <v/>
+      <c r="I153" s="1">
+        <v>0.17</v>
       </c>
       <c r="J153" t="str">
         <v>Legacy</v>
@@ -7619,7 +7619,7 @@
         <v>0.05</v>
       </c>
       <c r="I154" s="1">
-        <v>0.16666666666666666</v>
+        <v>0.15</v>
       </c>
       <c r="J154" t="str">
         <v>Legacy</v>
@@ -7666,7 +7666,7 @@
         <v>0.3</v>
       </c>
       <c r="I155" s="1">
-        <v>0.16666666666666666</v>
+        <v>0.17</v>
       </c>
       <c r="J155" t="str">
         <v>Yes</v>
@@ -7712,8 +7712,8 @@
       <c r="H156" s="1">
         <v>0.25</v>
       </c>
-      <c r="I156" t="str">
-        <v/>
+      <c r="I156" s="1">
+        <v>0.17</v>
       </c>
       <c r="J156" t="str">
         <v>Yes</v>
@@ -7853,8 +7853,8 @@
       <c r="H159" s="1">
         <v>0.1</v>
       </c>
-      <c r="I159" t="str">
-        <v/>
+      <c r="I159" s="1">
+        <v>0.17</v>
       </c>
       <c r="J159" t="str">
         <v>Yes</v>
@@ -7901,7 +7901,7 @@
         <v>0.05</v>
       </c>
       <c r="I160" s="1">
-        <v>0.16666666666666666</v>
+        <v>0.15</v>
       </c>
       <c r="J160" t="str">
         <v>Yes</v>
@@ -8088,8 +8088,8 @@
       <c r="H164" s="1">
         <v>0.15</v>
       </c>
-      <c r="I164" t="str">
-        <v/>
+      <c r="I164" s="1">
+        <v>0.2</v>
       </c>
       <c r="J164" t="str">
         <v>Yes</v>
@@ -8370,8 +8370,8 @@
       <c r="H170" s="1">
         <v>0.15</v>
       </c>
-      <c r="I170" t="str">
-        <v/>
+      <c r="I170" s="1">
+        <v>0.2</v>
       </c>
       <c r="J170" t="str">
         <v>Yes</v>
@@ -8605,8 +8605,8 @@
       <c r="H175" s="1">
         <v>0.15</v>
       </c>
-      <c r="I175" t="str">
-        <v/>
+      <c r="I175" s="1">
+        <v>0.2</v>
       </c>
       <c r="J175" t="str">
         <v>Yes</v>
@@ -8840,8 +8840,8 @@
       <c r="H180" s="1">
         <v>0.15</v>
       </c>
-      <c r="I180" t="str">
-        <v/>
+      <c r="I180" s="1">
+        <v>0.2</v>
       </c>
       <c r="J180" t="str">
         <v>Yes</v>
@@ -9122,8 +9122,8 @@
       <c r="H186" s="1">
         <v>0.15</v>
       </c>
-      <c r="I186" t="str">
-        <v/>
+      <c r="I186" s="1">
+        <v>0.2</v>
       </c>
       <c r="J186" t="str">
         <v>Yes</v>
@@ -9357,8 +9357,8 @@
       <c r="H191" s="1">
         <v>0.15</v>
       </c>
-      <c r="I191" t="str">
-        <v/>
+      <c r="I191" s="1">
+        <v>0.2</v>
       </c>
       <c r="J191" t="str">
         <v>Yes</v>
@@ -9639,8 +9639,8 @@
       <c r="H197" s="1">
         <v>0.15</v>
       </c>
-      <c r="I197" t="str">
-        <v/>
+      <c r="I197" s="1">
+        <v>0.2</v>
       </c>
       <c r="J197" t="str">
         <v>Yes</v>
@@ -9874,8 +9874,8 @@
       <c r="H202" s="1">
         <v>0.15</v>
       </c>
-      <c r="I202" t="str">
-        <v/>
+      <c r="I202" s="1">
+        <v>0.2</v>
       </c>
       <c r="J202" t="str">
         <v>Yes</v>
@@ -10109,8 +10109,8 @@
       <c r="H207" s="1">
         <v>0.15</v>
       </c>
-      <c r="I207" t="str">
-        <v/>
+      <c r="I207" s="1">
+        <v>0.2</v>
       </c>
       <c r="J207" t="str">
         <v>Yes</v>
@@ -10344,8 +10344,8 @@
       <c r="H212" s="1">
         <v>0.15</v>
       </c>
-      <c r="I212" t="str">
-        <v/>
+      <c r="I212" s="1">
+        <v>0.2</v>
       </c>
       <c r="J212" t="str">
         <v>Yes</v>
@@ -10579,8 +10579,8 @@
       <c r="H217" s="1">
         <v>0.15</v>
       </c>
-      <c r="I217" t="str">
-        <v/>
+      <c r="I217" s="1">
+        <v>0.2</v>
       </c>
       <c r="J217" t="str">
         <v>Yes</v>
@@ -10814,8 +10814,8 @@
       <c r="H222" s="1">
         <v>0.15</v>
       </c>
-      <c r="I222" t="str">
-        <v/>
+      <c r="I222" s="1">
+        <v>0.2</v>
       </c>
       <c r="J222" t="str">
         <v>Yes</v>
@@ -11096,8 +11096,8 @@
       <c r="H228" s="1">
         <v>0.15</v>
       </c>
-      <c r="I228" t="str">
-        <v/>
+      <c r="I228" s="1">
+        <v>0.2</v>
       </c>
       <c r="J228" t="str">
         <v>Yes</v>
@@ -11331,8 +11331,8 @@
       <c r="H233" s="1">
         <v>0.15</v>
       </c>
-      <c r="I233" t="str">
-        <v/>
+      <c r="I233" s="1">
+        <v>0.2</v>
       </c>
       <c r="J233" t="str">
         <v>Yes</v>
@@ -11566,8 +11566,8 @@
       <c r="H238" s="1">
         <v>0.15</v>
       </c>
-      <c r="I238" t="str">
-        <v/>
+      <c r="I238" s="1">
+        <v>0.2</v>
       </c>
       <c r="J238" t="str">
         <v>Yes</v>
@@ -11801,8 +11801,8 @@
       <c r="H243" s="1">
         <v>0.15</v>
       </c>
-      <c r="I243" t="str">
-        <v/>
+      <c r="I243" s="1">
+        <v>0.2</v>
       </c>
       <c r="J243" t="str">
         <v>Yes</v>
@@ -12036,8 +12036,8 @@
       <c r="H248" s="1">
         <v>0.15</v>
       </c>
-      <c r="I248" t="str">
-        <v/>
+      <c r="I248" s="1">
+        <v>0.2</v>
       </c>
       <c r="J248" t="str">
         <v>Yes</v>
@@ -12271,8 +12271,8 @@
       <c r="H253" s="1">
         <v>0.15</v>
       </c>
-      <c r="I253" t="str">
-        <v/>
+      <c r="I253" s="1">
+        <v>0.2</v>
       </c>
       <c r="J253" t="str">
         <v>Yes</v>
@@ -12506,8 +12506,8 @@
       <c r="H258" s="1">
         <v>0.15</v>
       </c>
-      <c r="I258" t="str">
-        <v/>
+      <c r="I258" s="1">
+        <v>0.2</v>
       </c>
       <c r="J258" t="str">
         <v>Yes</v>
@@ -12788,8 +12788,8 @@
       <c r="H264" s="1">
         <v>0.15</v>
       </c>
-      <c r="I264" t="str">
-        <v/>
+      <c r="I264" s="1">
+        <v>0.2</v>
       </c>
       <c r="J264" t="str">
         <v>Yes</v>
@@ -13023,8 +13023,8 @@
       <c r="H269" s="1">
         <v>0.15</v>
       </c>
-      <c r="I269" t="str">
-        <v/>
+      <c r="I269" s="1">
+        <v>0.2</v>
       </c>
       <c r="J269" t="str">
         <v>Yes</v>
@@ -13258,8 +13258,8 @@
       <c r="H274" s="1">
         <v>0.15</v>
       </c>
-      <c r="I274" t="str">
-        <v/>
+      <c r="I274" s="1">
+        <v>0.2</v>
       </c>
       <c r="J274" t="str">
         <v>Yes</v>
@@ -13493,8 +13493,8 @@
       <c r="H279" s="1">
         <v>0.15</v>
       </c>
-      <c r="I279" t="str">
-        <v/>
+      <c r="I279" s="1">
+        <v>0.2</v>
       </c>
       <c r="J279" t="str">
         <v>Yes</v>
@@ -13728,8 +13728,8 @@
       <c r="H284" s="1">
         <v>0.15</v>
       </c>
-      <c r="I284" t="str">
-        <v/>
+      <c r="I284" s="1">
+        <v>0.2</v>
       </c>
       <c r="J284" t="str">
         <v>Yes</v>
@@ -13823,7 +13823,7 @@
         <v>0.3</v>
       </c>
       <c r="I286" s="1">
-        <v>0.16666666666666666</v>
+        <v>0.17</v>
       </c>
       <c r="J286" t="str">
         <v>Yes</v>
@@ -13869,8 +13869,8 @@
       <c r="H287" s="1">
         <v>0.25</v>
       </c>
-      <c r="I287" t="str">
-        <v/>
+      <c r="I287" s="1">
+        <v>0.17</v>
       </c>
       <c r="J287" t="str">
         <v>Yes</v>
@@ -14010,8 +14010,8 @@
       <c r="H290" s="1">
         <v>0.1</v>
       </c>
-      <c r="I290" t="str">
-        <v/>
+      <c r="I290" s="1">
+        <v>0.17</v>
       </c>
       <c r="J290" t="str">
         <v>Yes</v>
@@ -14058,7 +14058,7 @@
         <v>0.05</v>
       </c>
       <c r="I291" s="1">
-        <v>0.16666666666666666</v>
+        <v>0.15</v>
       </c>
       <c r="J291" t="str">
         <v>Yes</v>
@@ -14105,7 +14105,7 @@
         <v>0.3</v>
       </c>
       <c r="I292" s="1">
-        <v>0.16666666666666666</v>
+        <v>0.17</v>
       </c>
       <c r="J292" t="str">
         <v>Yes</v>
@@ -14151,8 +14151,8 @@
       <c r="H293" s="1">
         <v>0.25</v>
       </c>
-      <c r="I293" t="str">
-        <v/>
+      <c r="I293" s="1">
+        <v>0.17</v>
       </c>
       <c r="J293" t="str">
         <v>Yes</v>
@@ -14292,8 +14292,8 @@
       <c r="H296" s="1">
         <v>0.1</v>
       </c>
-      <c r="I296" t="str">
-        <v/>
+      <c r="I296" s="1">
+        <v>0.17</v>
       </c>
       <c r="J296" t="str">
         <v>Yes</v>
@@ -14340,7 +14340,7 @@
         <v>0.05</v>
       </c>
       <c r="I297" s="1">
-        <v>0.16666666666666666</v>
+        <v>0.15</v>
       </c>
       <c r="J297" t="str">
         <v>Yes</v>
@@ -14387,7 +14387,7 @@
         <v>0.3</v>
       </c>
       <c r="I298" s="1">
-        <v>0.16666666666666666</v>
+        <v>0.17</v>
       </c>
       <c r="J298" t="str">
         <v>Yes</v>
@@ -14433,8 +14433,8 @@
       <c r="H299" s="1">
         <v>0.25</v>
       </c>
-      <c r="I299" t="str">
-        <v/>
+      <c r="I299" s="1">
+        <v>0.17</v>
       </c>
       <c r="J299" t="str">
         <v>Yes</v>
@@ -14574,8 +14574,8 @@
       <c r="H302" s="1">
         <v>0.1</v>
       </c>
-      <c r="I302" t="str">
-        <v/>
+      <c r="I302" s="1">
+        <v>0.17</v>
       </c>
       <c r="J302" t="str">
         <v>Yes</v>
@@ -14622,7 +14622,7 @@
         <v>0.05</v>
       </c>
       <c r="I303" s="1">
-        <v>0.16666666666666666</v>
+        <v>0.15</v>
       </c>
       <c r="J303" t="str">
         <v>Yes</v>
@@ -14809,8 +14809,8 @@
       <c r="H307" s="1">
         <v>0.15</v>
       </c>
-      <c r="I307" t="str">
-        <v/>
+      <c r="I307" s="1">
+        <v>0.2</v>
       </c>
       <c r="J307" t="str">
         <v>Yes</v>
@@ -15749,8 +15749,8 @@
       <c r="H327" s="1">
         <v>0.15</v>
       </c>
-      <c r="I327" t="str">
-        <v/>
+      <c r="I327" s="1">
+        <v>0.2</v>
       </c>
       <c r="J327" t="str">
         <v>Yes</v>
@@ -15984,8 +15984,8 @@
       <c r="H332" s="1">
         <v>0.15</v>
       </c>
-      <c r="I332" t="str">
-        <v/>
+      <c r="I332" s="1">
+        <v>0.2</v>
       </c>
       <c r="J332" t="str">
         <v>Yes</v>
@@ -16219,8 +16219,8 @@
       <c r="H337" s="1">
         <v>0.15</v>
       </c>
-      <c r="I337" t="str">
-        <v/>
+      <c r="I337" s="1">
+        <v>0.2</v>
       </c>
       <c r="J337" t="str">
         <v>Yes</v>
@@ -16454,8 +16454,8 @@
       <c r="H342" s="1">
         <v>0.15</v>
       </c>
-      <c r="I342" t="str">
-        <v/>
+      <c r="I342" s="1">
+        <v>0.2</v>
       </c>
       <c r="J342" t="str">
         <v>Yes</v>
@@ -16689,8 +16689,8 @@
       <c r="H347" s="1">
         <v>0.15</v>
       </c>
-      <c r="I347" t="str">
-        <v/>
+      <c r="I347" s="1">
+        <v>0.2</v>
       </c>
       <c r="J347" t="str">
         <v>Yes</v>
@@ -16924,8 +16924,8 @@
       <c r="H352" s="1">
         <v>0.15</v>
       </c>
-      <c r="I352" t="str">
-        <v/>
+      <c r="I352" s="1">
+        <v>0.2</v>
       </c>
       <c r="J352" t="str">
         <v>Yes</v>
@@ -17159,8 +17159,8 @@
       <c r="H357" s="1">
         <v>0.15</v>
       </c>
-      <c r="I357" t="str">
-        <v/>
+      <c r="I357" s="1">
+        <v>0.2</v>
       </c>
       <c r="J357" t="str">
         <v>Yes</v>
@@ -17253,8 +17253,8 @@
       <c r="H359" s="1">
         <v>0.33</v>
       </c>
-      <c r="I359" t="str">
-        <v/>
+      <c r="I359" s="1">
+        <v>0.33</v>
       </c>
       <c r="J359" t="str">
         <v>Yes</v>
@@ -17300,8 +17300,8 @@
       <c r="H360" s="1">
         <v>0.33</v>
       </c>
-      <c r="I360" t="str">
-        <v/>
+      <c r="I360" s="1">
+        <v>0.33</v>
       </c>
       <c r="J360" t="str">
         <v>Yes</v>
@@ -17347,8 +17347,8 @@
       <c r="H361" s="1">
         <v>0.33</v>
       </c>
-      <c r="I361" t="str">
-        <v/>
+      <c r="I361" s="1">
+        <v>0.34</v>
       </c>
       <c r="J361" t="str">
         <v>Yes</v>
@@ -17535,8 +17535,8 @@
       <c r="H365" s="1">
         <v>0.15</v>
       </c>
-      <c r="I365" t="str">
-        <v/>
+      <c r="I365" s="1">
+        <v>0.2</v>
       </c>
       <c r="J365" t="str">
         <v>Yes</v>
@@ -17770,8 +17770,8 @@
       <c r="H370" s="1">
         <v>0.15</v>
       </c>
-      <c r="I370" t="str">
-        <v/>
+      <c r="I370" s="1">
+        <v>0.2</v>
       </c>
       <c r="J370" t="str">
         <v>Yes</v>
@@ -18193,8 +18193,8 @@
       <c r="H379" s="1">
         <v>0.15</v>
       </c>
-      <c r="I379" t="str">
-        <v/>
+      <c r="I379" s="1">
+        <v>0.2</v>
       </c>
       <c r="J379" t="str">
         <v>Yes</v>
@@ -18428,8 +18428,8 @@
       <c r="H384" s="1">
         <v>0.15</v>
       </c>
-      <c r="I384" t="str">
-        <v/>
+      <c r="I384" s="1">
+        <v>0.2</v>
       </c>
       <c r="J384" t="str">
         <v>Yes</v>
@@ -18663,8 +18663,8 @@
       <c r="H389" s="1">
         <v>0.15</v>
       </c>
-      <c r="I389" t="str">
-        <v/>
+      <c r="I389" s="1">
+        <v>0.2</v>
       </c>
       <c r="J389" t="str">
         <v>Yes</v>
@@ -19086,8 +19086,8 @@
       <c r="H398" s="1">
         <v>0.15</v>
       </c>
-      <c r="I398" t="str">
-        <v/>
+      <c r="I398" s="1">
+        <v>0.2</v>
       </c>
       <c r="J398" t="str">
         <v>Yes</v>
@@ -19321,8 +19321,8 @@
       <c r="H403" s="1">
         <v>0.15</v>
       </c>
-      <c r="I403" t="str">
-        <v/>
+      <c r="I403" s="1">
+        <v>0.2</v>
       </c>
       <c r="J403" t="str">
         <v>Yes</v>
@@ -19556,8 +19556,8 @@
       <c r="H408" s="1">
         <v>0.15</v>
       </c>
-      <c r="I408" t="str">
-        <v/>
+      <c r="I408" s="1">
+        <v>0.2</v>
       </c>
       <c r="J408" t="str">
         <v>Yes</v>
@@ -19741,8 +19741,8 @@
       <c r="H412" s="1">
         <v>0.33</v>
       </c>
-      <c r="I412" t="str">
-        <v/>
+      <c r="I412" s="1">
+        <v>0.33</v>
       </c>
       <c r="J412" t="str">
         <v>Yes</v>
@@ -19788,8 +19788,8 @@
       <c r="H413" s="1">
         <v>0.33</v>
       </c>
-      <c r="I413" t="str">
-        <v/>
+      <c r="I413" s="1">
+        <v>0.33</v>
       </c>
       <c r="J413" t="str">
         <v>Yes</v>
@@ -19835,8 +19835,8 @@
       <c r="H414" s="1">
         <v>0.33</v>
       </c>
-      <c r="I414" t="str">
-        <v/>
+      <c r="I414" s="1">
+        <v>0.34</v>
       </c>
       <c r="J414" t="str">
         <v>Yes</v>
